--- a/sample/menu sample/메뉴트리 샘플.xlsx
+++ b/sample/menu sample/메뉴트리 샘플.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inuackr-my.sharepoint.com/personal/hojun7766_inu_ac_kr/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hojun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69F1012D-B2D2-42FA-8BDB-E5262E52D36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A20AD5-0756-40C1-91D1-798032248BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F5287B75-BF32-4E4F-8178-9DAA85D4ECBC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1EF963A7-6703-46F9-A786-DC6D9D03D2A8}"/>
   </bookViews>
   <sheets>
     <sheet name="메뉴트리" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="262">
   <si>
     <t>1depth</t>
   </si>
@@ -742,6 +741,84 @@
   </si>
   <si>
     <t>토큰 폐기 기능</t>
+  </si>
+  <si>
+    <t>NeoFlow Studio</t>
+  </si>
+  <si>
+    <t>상단 메뉴</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>프로젝트 및 Job 패키지를 가져오거나 내보내는 기능</t>
+  </si>
+  <si>
+    <t>Window</t>
+  </si>
+  <si>
+    <t>Preferences</t>
+  </si>
+  <si>
+    <t>NeoFlow Server 접속 URL 및 API 토큰을 설정하는 기능</t>
+  </si>
+  <si>
+    <t>Help</t>
+  </si>
+  <si>
+    <t>Studio 라이선스를 등록하고 확인하는 기능</t>
+  </si>
+  <si>
+    <t>Repository 뷰</t>
+  </si>
+  <si>
+    <t>Job Designs</t>
+  </si>
+  <si>
+    <t>우클릭 메뉴</t>
+  </si>
+  <si>
+    <t>Import items</t>
+  </si>
+  <si>
+    <t>외부 Job 패키지 압축 파일을 로컬로 가져오는 기능</t>
+  </si>
+  <si>
+    <t>Sync to NeoFlow Server</t>
+  </si>
+  <si>
+    <t>선택한 Job을 NeoFlow Server로 동기화하는 기능</t>
+  </si>
+  <si>
+    <t>Create job</t>
+  </si>
+  <si>
+    <t>신규 Job 작업을 위한 빈 캔버스를 생성하는 기능</t>
+  </si>
+  <si>
+    <t>하단 뷰</t>
+  </si>
+  <si>
+    <t>Run job 탭</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>로컬 환경에서 현재 Job을 즉시 실행하는 기능</t>
+  </si>
+  <si>
+    <t>Kill</t>
+  </si>
+  <si>
+    <t>로컬에서 실행 중인 Job 프로세스를 강제 중지하는 기능</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>콘솔 창의 실행 로그 텍스트를 지우는 기능</t>
   </si>
   <si>
     <t>.</t>
@@ -898,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -929,6 +1006,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1244,13 +1324,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAD2F0E-22C4-4A40-90E6-44B3CFB2B20C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFAFF2C7-83A1-463A-B03F-34582D8E9728}">
   <sheetPr>
     <tabColor rgb="FF4A86E8"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -3397,15 +3477,189 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="6:6" ht="13.5">
-      <c r="F130" s="13" t="s">
+    <row r="126" spans="1:7" ht="13.5">
+      <c r="A126" s="3" t="s">
         <v>235</v>
       </c>
+      <c r="B126" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="13.5">
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="13.5">
+      <c r="A128" s="9"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A129" s="9"/>
+      <c r="B129" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="12.75" customHeight="1">
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="13.5">
+      <c r="A131" s="9"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="13.5">
+      <c r="A132" s="9"/>
+      <c r="B132" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="13.5">
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="13.5">
+      <c r="A134" s="10"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="13.5">
+      <c r="F139" s="14" t="s">
+        <v>261</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="49">
+    <mergeCell ref="D129:D131"/>
+    <mergeCell ref="B132:B134"/>
+    <mergeCell ref="C132:C134"/>
     <mergeCell ref="C118:C123"/>
     <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A126:A134"/>
+    <mergeCell ref="B126:B128"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="C129:C131"/>
     <mergeCell ref="D98:D99"/>
     <mergeCell ref="D100:D102"/>
     <mergeCell ref="D103:D105"/>
@@ -3449,7 +3703,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G125" xr:uid="{22C01893-16C9-417E-864B-C5A4A8B00640}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G134" xr:uid="{B44AACF0-C1FA-4C09-98C6-5BE0FEFDCDDD}">
       <formula1>"로그인,주요기능,부가기능,CRUD"</formula1>
     </dataValidation>
   </dataValidations>
